--- a/daily_analysis_combined.xlsx
+++ b/daily_analysis_combined.xlsx
@@ -425,449 +425,534 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>action</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>unit_value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>day1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>day2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>day3</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>day4</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>day5</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>day6</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>day7</t>
+          <t>main_level</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>buy</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>218.76</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>205.62</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>195</v>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>sub_bucket_1</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>sub_bucket_2</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>sub_bucket_3</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>sub_bucket_4</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>sub_bucket_5</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>sub_bucket_6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>184.38</v>
+      </c>
+      <c r="C6" t="n">
+        <v>150</v>
+      </c>
+      <c r="D6" t="n">
         <v>128.76</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>stop_loss_hit</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>trade_closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>buy</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="E6" t="n">
         <v>115.62</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>stop_loss_hit</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>buy</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="F6" t="n">
+        <v>105</v>
+      </c>
+      <c r="G6" t="n">
         <v>94.38</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>stop_loss_hit</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>buy</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="H6" t="n">
         <v>79.25999999999999</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>stop_loss_hit</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>main_level</t>
-        </is>
+      <c r="A7" t="n">
+        <v>171.24</v>
+      </c>
+      <c r="C7" t="n">
+        <v>144.98736</v>
+      </c>
+      <c r="D7" t="n">
+        <v>125.65896</v>
+      </c>
+      <c r="E7" t="n">
+        <v>113.11368</v>
+      </c>
+      <c r="F7" t="n">
+        <v>102.49368</v>
+      </c>
+      <c r="G7" t="n">
+        <v>90.81168</v>
+      </c>
+      <c r="H7" t="n">
+        <v>74.71463999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>240</v>
+        <v>150</v>
+      </c>
+      <c r="C8" t="n">
+        <v>141.88632</v>
+      </c>
+      <c r="D8" t="n">
+        <v>123.74052</v>
+      </c>
+      <c r="E8" t="n">
+        <v>111.56316</v>
+      </c>
+      <c r="F8" t="n">
+        <v>100.94316</v>
+      </c>
+      <c r="G8" t="n">
+        <v>88.60415999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>71.90267999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>218.76</v>
+        <v>128.76</v>
+      </c>
+      <c r="C9" t="n">
+        <v>139.38</v>
+      </c>
+      <c r="D9" t="n">
+        <v>122.19</v>
+      </c>
+      <c r="E9" t="n">
+        <v>110.31</v>
+      </c>
+      <c r="F9" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="G9" t="n">
+        <v>86.81999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>69.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>205.62</v>
+        <v>115.62</v>
+      </c>
+      <c r="C10" t="n">
+        <v>136.87368</v>
+      </c>
+      <c r="D10" t="n">
+        <v>120.63948</v>
+      </c>
+      <c r="E10" t="n">
+        <v>109.05684</v>
+      </c>
+      <c r="F10" t="n">
+        <v>98.43684</v>
+      </c>
+      <c r="G10" t="n">
+        <v>85.03583999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>67.35732</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>195</v>
+        <v>105</v>
+      </c>
+      <c r="C11" t="n">
+        <v>133.30536</v>
+      </c>
+      <c r="D11" t="n">
+        <v>118.43196</v>
+      </c>
+      <c r="E11" t="n">
+        <v>107.27268</v>
+      </c>
+      <c r="F11" t="n">
+        <v>96.65268</v>
+      </c>
+      <c r="G11" t="n">
+        <v>82.49567999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>64.12164</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>184.38</v>
+        <v>94.38</v>
+      </c>
+      <c r="C12" t="n">
+        <v>128.76</v>
+      </c>
+      <c r="D12" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="E12" t="n">
+        <v>105</v>
+      </c>
+      <c r="F12" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="G12" t="n">
+        <v>79.25999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>171.24</v>
+        <v>79.25999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128.76</v>
+        <v>38.76000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115.62</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94.38</v>
+        <v>4.379999999999995</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>-8.759999999999991</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>unit_value</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>day1</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>day2</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>day3</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>day4</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>day5</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>day6</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>day7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>128.76</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>buy_triggered</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>stop_loss_hit</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>buy_triggered</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>buy_triggered</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>stop_loss_hit</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>buy_triggered</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>stop_loss_hit</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
         <v>79.25999999999999</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>38.76000000000001</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>25.62</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>4.379999999999995</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>-8.759999999999991</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>stop_loss_hit</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>-30</v>
+      <c r="D26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>02/07/2024</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>03/07/2024</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>04/07/2024</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>05/07/2024</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>06/07/2024</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>07/07/2024</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>08/07/2024</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>sub_bucket_1</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>sub_bucket_2</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>sub_bucket_3</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>sub_bucket_4</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>sub_bucket_5</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>sub_bucket_6</t>
-        </is>
+      <c r="D28" t="n">
+        <v>151</v>
+      </c>
+      <c r="E28" t="n">
+        <v>130</v>
+      </c>
+      <c r="F28" t="n">
+        <v>115</v>
+      </c>
+      <c r="G28" t="n">
+        <v>105</v>
+      </c>
+      <c r="H28" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" t="n">
+        <v>95</v>
+      </c>
+      <c r="J28" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>150</v>
-      </c>
-      <c r="B29" t="n">
-        <v>128.76</v>
-      </c>
-      <c r="C29" t="n">
-        <v>115.62</v>
-      </c>
       <c r="D29" t="n">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="E29" t="n">
-        <v>94.38</v>
+        <v>125</v>
       </c>
       <c r="F29" t="n">
-        <v>79.25999999999999</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>144.98736</v>
-      </c>
-      <c r="B30" t="n">
-        <v>125.65896</v>
-      </c>
-      <c r="C30" t="n">
-        <v>113.11368</v>
-      </c>
-      <c r="D30" t="n">
-        <v>102.49368</v>
-      </c>
-      <c r="E30" t="n">
-        <v>90.81168</v>
-      </c>
-      <c r="F30" t="n">
-        <v>74.71463999999999</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>141.88632</v>
-      </c>
-      <c r="B31" t="n">
-        <v>123.74052</v>
-      </c>
-      <c r="C31" t="n">
-        <v>111.56316</v>
-      </c>
-      <c r="D31" t="n">
-        <v>100.94316</v>
-      </c>
-      <c r="E31" t="n">
-        <v>88.60415999999999</v>
-      </c>
-      <c r="F31" t="n">
-        <v>71.90267999999999</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>139.38</v>
-      </c>
-      <c r="B32" t="n">
-        <v>122.19</v>
-      </c>
-      <c r="C32" t="n">
-        <v>110.31</v>
-      </c>
-      <c r="D32" t="n">
-        <v>99.69</v>
-      </c>
-      <c r="E32" t="n">
-        <v>86.81999999999999</v>
-      </c>
-      <c r="F32" t="n">
-        <v>69.63</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>136.87368</v>
-      </c>
-      <c r="B33" t="n">
-        <v>120.63948</v>
-      </c>
-      <c r="C33" t="n">
-        <v>109.05684</v>
-      </c>
-      <c r="D33" t="n">
-        <v>98.43684</v>
-      </c>
-      <c r="E33" t="n">
-        <v>85.03583999999999</v>
-      </c>
-      <c r="F33" t="n">
-        <v>67.35732</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>133.30536</v>
-      </c>
-      <c r="B34" t="n">
-        <v>118.43196</v>
-      </c>
-      <c r="C34" t="n">
-        <v>107.27268</v>
-      </c>
-      <c r="D34" t="n">
-        <v>96.65268</v>
-      </c>
-      <c r="E34" t="n">
-        <v>82.49567999999999</v>
-      </c>
-      <c r="F34" t="n">
-        <v>64.12164</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>128.76</v>
-      </c>
-      <c r="B35" t="n">
-        <v>115.62</v>
-      </c>
-      <c r="C35" t="n">
-        <v>105</v>
-      </c>
-      <c r="D35" t="n">
-        <v>94.38</v>
-      </c>
-      <c r="E35" t="n">
-        <v>79.25999999999999</v>
-      </c>
-      <c r="F35" t="n">
-        <v>60</v>
+        <v>110</v>
+      </c>
+      <c r="G29" t="n">
+        <v>97</v>
+      </c>
+      <c r="H29" t="n">
+        <v>92</v>
+      </c>
+      <c r="I29" t="n">
+        <v>85</v>
+      </c>
+      <c r="J29" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/daily_analysis_combined.xlsx
+++ b/daily_analysis_combined.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eeuma\Desktop\students_clients_data\Lorenzo\trading_webapp\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007E0CB4-F594-4CCB-A27F-EF05A2B80173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="fib_buy_sell" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="fib_buy_sell"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -112,8 +106,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,7 +119,15 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -135,7 +138,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -145,40 +148,71 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="11">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -189,10 +223,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -230,69 +264,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -316,54 +352,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -373,7 +408,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -382,7 +417,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -391,7 +426,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -399,10 +434,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -431,7 +466,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -444,13 +479,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -468,43 +502,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="8" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="4.576428571428571" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="5">
         <v>240</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="6">
         <v>218.76</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="6">
         <v>205.62</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="5">
         <v>195</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="7" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -522,216 +600,335 @@
       <c r="H5" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="6">
         <v>184.38</v>
       </c>
-      <c r="C6">
+      <c r="B6" s="2"/>
+      <c r="C6" s="5">
         <v>150</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="6">
         <v>128.76</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="6">
         <v>115.62</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="5">
         <v>105</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="6">
         <v>94.38</v>
       </c>
-      <c r="H6">
-        <v>79.259999999999991</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="H6" s="6">
+        <v>79.25999999999999</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="6">
         <v>171.24</v>
       </c>
-      <c r="C7">
+      <c r="B7" s="2"/>
+      <c r="C7" s="6">
         <v>144.98736</v>
       </c>
-      <c r="D7">
-        <v>125.65895999999999</v>
-      </c>
-      <c r="E7">
+      <c r="D7" s="6">
+        <v>125.65896</v>
+      </c>
+      <c r="E7" s="6">
         <v>113.11368</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="6">
         <v>102.49368</v>
       </c>
-      <c r="G7">
-        <v>90.811679999999996</v>
-      </c>
-      <c r="H7">
-        <v>74.714639999999989</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="G7" s="6">
+        <v>90.81168</v>
+      </c>
+      <c r="H7" s="6">
+        <v>74.71463999999999</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="5">
         <v>150</v>
       </c>
-      <c r="C8">
-        <v>141.88632000000001</v>
-      </c>
-      <c r="D8">
+      <c r="B8" s="2"/>
+      <c r="C8" s="6">
+        <v>141.88632</v>
+      </c>
+      <c r="D8" s="6">
         <v>123.74052</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="6">
         <v>111.56316</v>
       </c>
-      <c r="F8">
-        <v>100.94316000000001</v>
-      </c>
-      <c r="G8">
-        <v>88.604159999999993</v>
-      </c>
-      <c r="H8">
-        <v>71.902679999999989</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="F8" s="6">
+        <v>100.94316</v>
+      </c>
+      <c r="G8" s="6">
+        <v>88.60416</v>
+      </c>
+      <c r="H8" s="6">
+        <v>71.90267999999999</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="6">
         <v>128.76</v>
       </c>
-      <c r="C9">
+      <c r="B9" s="2"/>
+      <c r="C9" s="6">
         <v>139.38</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="6">
         <v>122.19</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="6">
         <v>110.31</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="6">
         <v>99.69</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="6">
         <v>86.82</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="6">
         <v>69.63</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="6">
         <v>115.62</v>
       </c>
-      <c r="C10">
-        <v>136.87368000000001</v>
-      </c>
-      <c r="D10">
-        <v>120.63948000000001</v>
-      </c>
-      <c r="E10">
-        <v>109.05683999999999</v>
-      </c>
-      <c r="F10">
-        <v>98.436840000000004</v>
-      </c>
-      <c r="G10">
-        <v>85.035839999999993</v>
-      </c>
-      <c r="H10">
-        <v>67.357320000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="B10" s="2"/>
+      <c r="C10" s="6">
+        <v>136.87368</v>
+      </c>
+      <c r="D10" s="6">
+        <v>120.63948</v>
+      </c>
+      <c r="E10" s="6">
+        <v>109.05684</v>
+      </c>
+      <c r="F10" s="6">
+        <v>98.43684</v>
+      </c>
+      <c r="G10" s="6">
+        <v>85.03584</v>
+      </c>
+      <c r="H10" s="6">
+        <v>67.35732</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="5">
         <v>105</v>
       </c>
-      <c r="C11">
-        <v>133.30536000000001</v>
-      </c>
-      <c r="D11">
+      <c r="B11" s="2"/>
+      <c r="C11" s="6">
+        <v>133.30536</v>
+      </c>
+      <c r="D11" s="6">
         <v>118.43196</v>
       </c>
-      <c r="E11">
-        <v>107.27267999999999</v>
-      </c>
-      <c r="F11">
-        <v>96.652680000000004</v>
-      </c>
-      <c r="G11">
-        <v>82.495679999999993</v>
-      </c>
-      <c r="H11">
-        <v>64.121639999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="E11" s="6">
+        <v>107.27268</v>
+      </c>
+      <c r="F11" s="6">
+        <v>96.65268</v>
+      </c>
+      <c r="G11" s="6">
+        <v>82.49568</v>
+      </c>
+      <c r="H11" s="6">
+        <v>64.12164</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="6">
         <v>94.38</v>
       </c>
-      <c r="C12">
+      <c r="B12" s="2"/>
+      <c r="C12" s="6">
         <v>128.76</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="6">
         <v>115.62</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="5">
         <v>105</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="6">
         <v>94.38</v>
       </c>
-      <c r="G12">
-        <v>79.259999999999991</v>
-      </c>
-      <c r="H12">
+      <c r="G12" s="6">
+        <v>79.25999999999999</v>
+      </c>
+      <c r="H12" s="5">
         <v>60</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>79.259999999999991</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="6">
+        <v>79.25999999999999</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="5">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>38.760000000000012</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="B14" s="2"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="6">
+        <v>38.76000000000001</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="6">
         <v>25.62</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="B16" s="2"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="5">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>4.3799999999999946</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>-8.7599999999999909</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="B17" s="2"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="6">
+        <v>4.379999999999995</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="6">
+        <v>-8.759999999999991</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="5">
         <v>-30</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="2"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="4"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="4"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20.25">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -756,78 +953,112 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="5">
         <v>1</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="6">
         <v>128.76</v>
       </c>
-      <c r="E24" t="s">
+      <c r="D24" s="4"/>
+      <c r="E24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I24" t="s">
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="5">
         <v>2</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="6">
         <v>115.62</v>
       </c>
-      <c r="F25" t="s">
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I25" t="s">
+      <c r="H25" s="4"/>
+      <c r="I25" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="J25" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="5">
         <v>2</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="6">
         <v>94.38</v>
       </c>
-      <c r="H26" t="s">
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="J26" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="5">
         <v>1</v>
       </c>
-      <c r="C27">
-        <v>79.259999999999991</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="C27" s="6">
+        <v>79.25999999999999</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="4"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="3"/>
       <c r="D29" s="1">
         <v>0</v>
       </c>
@@ -850,83 +1081,104 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D30" t="s">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="4"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D31">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="4"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="5">
         <v>151</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="5">
         <v>130</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="5">
         <v>115</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="5">
         <v>105</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="5">
         <v>100</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="5">
         <v>95</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="5">
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D32">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="4"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="5">
         <v>148</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="5">
         <v>125</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="5">
         <v>110</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="5">
         <v>97</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="5">
         <v>92</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="5">
         <v>85</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="5">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="4"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="20.25">
       <c r="A34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -951,66 +1203,89 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="5">
         <v>1</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="6">
         <v>128.76</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="5">
         <v>2</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="6">
         <v>115.62</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="5">
         <v>2</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="6">
         <v>94.38</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="5">
         <v>1</v>
       </c>
-      <c r="C38">
-        <v>79.259999999999991</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="6">
+        <v>79.25999999999999</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/daily_analysis_combined.xlsx
+++ b/daily_analysis_combined.xlsx
@@ -757,8 +757,10 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
-        <v>102.49368</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>102.49368 stop_loss</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -780,17 +782,17 @@
       <c r="C25" t="n">
         <v>115.62</v>
       </c>
-      <c r="D25" t="n">
-        <v>150</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>buy_triggered</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>102.49368</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>102.49368 stop_loss</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -808,12 +810,8 @@
       <c r="C26" t="n">
         <v>94.38</v>
       </c>
-      <c r="D26" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="E26" t="n">
-        <v>69.63</v>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -832,9 +830,7 @@
       <c r="C27" t="n">
         <v>79.25999999999999</v>
       </c>
-      <c r="D27" t="n">
-        <v>105</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>

--- a/daily_analysis_combined.xlsx
+++ b/daily_analysis_combined.xlsx
@@ -765,7 +765,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>102.49368 stop_loss_1 | trade_closed</t>
+          <t>102.49368 stop_loss_1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -808,14 +808,10 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>102.49368 stop_loss_2_1 | trade_closed</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>trade_closed</t>
-        </is>
-      </c>
+          <t>150.0 sell_profit_2_1</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>trade_closed</t>
@@ -853,7 +849,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>90.81168 stop_loss_2_2 | trade_closed</t>
+          <t>90.81168 stop_loss_2_2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1012,7 +1008,7 @@
         <v>115</v>
       </c>
       <c r="H33" t="n">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="I33" t="n">
         <v>100</v>

--- a/daily_analysis_combined.xlsx
+++ b/daily_analysis_combined.xlsx
@@ -849,7 +849,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>90.81168 stop_loss_2_2</t>
+          <t>171.24 sell_profit_2_2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -882,8 +882,16 @@
           <t>buy_triggered</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>128.76 sell_profit_3_1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -909,8 +917,16 @@
           <t>buy_triggered</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>115.62 sell_profit_3_2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1014,7 +1030,7 @@
         <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="K33" t="n">
         <v>75</v>

--- a/daily_analysis_combined.xlsx
+++ b/daily_analysis_combined.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="33">
       <c r="E33" t="n">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="G33" t="n">
         <v>115</v>
@@ -1175,6 +1175,455 @@
       </c>
       <c r="D42" t="n">
         <v>60</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>sub_unit</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>unit_value</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>day1</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>day2</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>day3</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>day4</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>day5</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>day6</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="inlineStr">
+        <is>
+          <t>day7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>128.76</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>sell_triggered</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>115.62 buyback_profit_1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>sell_triggered</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>105.0 buyback_profit_2_1</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>sell_triggered</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>150.0 stop_loss_2_2</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>sell_triggered</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>105.0 stop_loss_3_1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>sell_triggered</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>115.62 stop_loss_3_2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>79.25999999999999</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>sell_triggered</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>94.38 stop_loss_4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>u1_1</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>128.76</v>
+      </c>
+      <c r="C53" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="D53" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>u2_2_1</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="C54" t="n">
+        <v>105</v>
+      </c>
+      <c r="D54" t="n">
+        <v>128.76</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>u2_2_2</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="C55" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="D55" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>u3_2_1</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="C56" t="n">
+        <v>79.25999999999999</v>
+      </c>
+      <c r="D56" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>u3_2_2</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="C57" t="n">
+        <v>60</v>
+      </c>
+      <c r="D57" t="n">
+        <v>115.62</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>u1_4</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>79.25999999999999</v>
+      </c>
+      <c r="C58" t="n">
+        <v>60</v>
+      </c>
+      <c r="D58" t="n">
+        <v>94.38</v>
       </c>
     </row>
   </sheetData>

--- a/daily_analysis_combined.xlsx
+++ b/daily_analysis_combined.xlsx
@@ -1154,11 +1154,6 @@
           <t>day7</t>
         </is>
       </c>
-      <c r="U59" s="1" t="inlineStr">
-        <is>
-          <t>pnl_point</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>332.38079999999997 buy_profit_1 ( error1)</t>
+          <t>329.0192 buyback_profit_1</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -1223,9 +1218,6 @@
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="n">
-        <v>-2.719199999999944</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1281,24 +1273,13 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>330.7 buy_profit_2_1 ( error1)</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>trade_closed</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>trade_closed</t>
-        </is>
-      </c>
+          <t>328.5 buyback_profit_2_1 ( error1)</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="n">
-        <v>-1.680799999999977</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1352,26 +1333,11 @@
           <t>sell_triggered</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>331.73839999999996 buy_profit_2_2 ( error1)</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>trade_closed</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>trade_closed</t>
-        </is>
-      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
-        <v>-2.719199999999944</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1426,7 +1392,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>329.6616 buy_profit_3_1 ( error1)</t>
+          <t>328.5 stop_loss_3_1</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -1446,9 +1412,6 @@
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="n">
-        <v>-1.680800000000033</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1503,7 +1466,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>329.0192 buy_profit_3_2 ( error1)</t>
+          <t>329.0192 stop_loss_3_2</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -1523,9 +1486,6 @@
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="n">
-        <v>-1.038400000000024</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1578,7 +1538,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>328.5 buy_profit_4 ( error1)</t>
+          <t>327.9808 stop_loss_4</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -1598,9 +1558,6 @@
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="n">
-        <v>-1.258399999999995</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1634,97 +1591,97 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>d1_1</t>
+          <t>u1_1</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>329.6616</v>
       </c>
       <c r="C68" t="n">
-        <v>332.3808</v>
+        <v>329.0192</v>
       </c>
       <c r="D68" t="n">
-        <v>328.3774688</v>
+        <v>330.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>d2_2_1</t>
+          <t>u2_2_1</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>329.0192</v>
       </c>
       <c r="C69" t="n">
-        <v>330.7</v>
+        <v>328.5</v>
       </c>
       <c r="D69" t="n">
-        <v>328.3774688</v>
+        <v>329.6616</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>d2_2_2</t>
+          <t>u2_2_2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>329.0192</v>
       </c>
       <c r="C70" t="n">
-        <v>331.7384</v>
+        <v>327.9808</v>
       </c>
       <c r="D70" t="n">
-        <v>327.8063488</v>
+        <v>330.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>d3_2_1</t>
+          <t>u3_2_1</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>327.9808</v>
       </c>
       <c r="C71" t="n">
-        <v>329.6616</v>
+        <v>327.2416</v>
       </c>
       <c r="D71" t="n">
-        <v>326.7708</v>
+        <v>328.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>d3_2_2</t>
+          <t>u3_2_2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>327.9808</v>
       </c>
       <c r="C72" t="n">
+        <v>326.3</v>
+      </c>
+      <c r="D72" t="n">
         <v>329.0192</v>
-      </c>
-      <c r="D72" t="n">
-        <v>326.7708</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>d1_4</t>
+          <t>u1_4</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>327.2416</v>
       </c>
       <c r="C73" t="n">
-        <v>328.5</v>
+        <v>326.3</v>
       </c>
       <c r="D73" t="n">
-        <v>326.3</v>
+        <v>327.9808</v>
       </c>
     </row>
     <row r="74">
@@ -8374,11 +8331,6 @@
           <t>day7</t>
         </is>
       </c>
-      <c r="U449" s="1" t="inlineStr">
-        <is>
-          <t>pnl_point</t>
-        </is>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -8431,11 +8383,6 @@
       <c r="R450" t="inlineStr"/>
       <c r="S450" t="inlineStr"/>
       <c r="T450" t="inlineStr"/>
-      <c r="U450" t="inlineStr">
-        <is>
-          <t>trade_not_closed</t>
-        </is>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -8494,11 +8441,6 @@
       </c>
       <c r="S451" t="inlineStr"/>
       <c r="T451" t="inlineStr"/>
-      <c r="U451" t="inlineStr">
-        <is>
-          <t>trade_not_closed</t>
-        </is>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -8557,11 +8499,6 @@
       </c>
       <c r="S452" t="inlineStr"/>
       <c r="T452" t="inlineStr"/>
-      <c r="U452" t="inlineStr">
-        <is>
-          <t>trade_not_closed</t>
-        </is>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -8617,7 +8554,7 @@
       </c>
       <c r="P453" t="inlineStr">
         <is>
-          <t>331.6032 buy_profit_3_1 ( error1)</t>
+          <t>329.5132 buyback_profit_3_1 ( error1)</t>
         </is>
       </c>
       <c r="Q453" t="inlineStr">
@@ -8632,9 +8569,6 @@
       </c>
       <c r="S453" t="inlineStr"/>
       <c r="T453" t="inlineStr"/>
-      <c r="U453" t="n">
-        <v>-1.451600000000042</v>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -8688,14 +8622,10 @@
           <t>sell_triggered</t>
         </is>
       </c>
-      <c r="P454" t="inlineStr">
-        <is>
-          <t>331.0484 buy_profit_3_2 ( error1)</t>
-        </is>
-      </c>
+      <c r="P454" t="inlineStr"/>
       <c r="Q454" t="inlineStr">
         <is>
-          <t>trade_closed</t>
+          <t>328.7 buyback_profit_3_2</t>
         </is>
       </c>
       <c r="R454" t="inlineStr">
@@ -8705,9 +8635,6 @@
       </c>
       <c r="S454" t="inlineStr"/>
       <c r="T454" t="inlineStr"/>
-      <c r="U454" t="n">
-        <v>-0.8968000000000416</v>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -8760,7 +8687,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>330.6 buy_profit_4 ( error1)</t>
+          <t>330.1516 stop_loss_4</t>
         </is>
       </c>
       <c r="P455" t="inlineStr">
@@ -8780,9 +8707,6 @@
       </c>
       <c r="S455" t="inlineStr"/>
       <c r="T455" t="inlineStr"/>
-      <c r="U455" t="n">
-        <v>-1.086800000000039</v>
-      </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="inlineStr">
@@ -8816,97 +8740,97 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>d1_1</t>
+          <t>u1_1</t>
         </is>
       </c>
       <c r="B458" t="n">
         <v>331.6032</v>
       </c>
       <c r="C458" t="n">
-        <v>333.9516</v>
+        <v>331.0484</v>
       </c>
       <c r="D458" t="n">
-        <v>330.4941776</v>
+        <v>332.5</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>d2_2_1</t>
+          <t>u2_2_1</t>
         </is>
       </c>
       <c r="B459" t="n">
         <v>331.0484</v>
       </c>
       <c r="C459" t="n">
-        <v>332.5</v>
+        <v>330.6</v>
       </c>
       <c r="D459" t="n">
-        <v>330.4941776</v>
+        <v>331.6032</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>d2_2_2</t>
+          <t>u2_2_2</t>
         </is>
       </c>
       <c r="B460" t="n">
         <v>331.0484</v>
       </c>
       <c r="C460" t="n">
-        <v>333.3968</v>
+        <v>330.1516</v>
       </c>
       <c r="D460" t="n">
-        <v>330.0009376</v>
+        <v>332.5</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>d3_2_1</t>
+          <t>u3_2_1</t>
         </is>
       </c>
       <c r="B461" t="n">
         <v>330.1516</v>
       </c>
       <c r="C461" t="n">
-        <v>331.6032</v>
+        <v>329.5132</v>
       </c>
       <c r="D461" t="n">
-        <v>329.1066</v>
+        <v>330.6</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>d3_2_2</t>
+          <t>u3_2_2</t>
         </is>
       </c>
       <c r="B462" t="n">
         <v>330.1516</v>
       </c>
       <c r="C462" t="n">
+        <v>328.7</v>
+      </c>
+      <c r="D462" t="n">
         <v>331.0484</v>
-      </c>
-      <c r="D462" t="n">
-        <v>329.1066</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>d1_4</t>
+          <t>u1_4</t>
         </is>
       </c>
       <c r="B463" t="n">
         <v>329.5132</v>
       </c>
       <c r="C463" t="n">
-        <v>330.6</v>
+        <v>328.7</v>
       </c>
       <c r="D463" t="n">
-        <v>328.7</v>
+        <v>330.1516</v>
       </c>
     </row>
     <row r="464">

--- a/daily_analysis_combined.xlsx
+++ b/daily_analysis_combined.xlsx
@@ -1154,6 +1154,11 @@
           <t>day7</t>
         </is>
       </c>
+      <c r="U59" s="1" t="inlineStr">
+        <is>
+          <t>pnl_point</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1218,6 +1223,9 @@
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
+      <c r="U60" t="n">
+        <v>0.6424000000000092</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1280,6 +1288,9 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>0.5192000000000121</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1338,6 +1349,11 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>trade_not_closed</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1412,6 +1428,9 @@
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
+      <c r="U63" t="n">
+        <v>-0.5192000000000121</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1486,6 +1505,9 @@
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
+      <c r="U64" t="n">
+        <v>-1.038400000000024</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1558,6 +1580,9 @@
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
+      <c r="U65" t="n">
+        <v>-0.7391999999999825</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -8331,6 +8356,11 @@
           <t>day7</t>
         </is>
       </c>
+      <c r="U449" s="1" t="inlineStr">
+        <is>
+          <t>pnl_point</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -8383,6 +8413,11 @@
       <c r="R450" t="inlineStr"/>
       <c r="S450" t="inlineStr"/>
       <c r="T450" t="inlineStr"/>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>trade_not_closed</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -8441,6 +8476,11 @@
       </c>
       <c r="S451" t="inlineStr"/>
       <c r="T451" t="inlineStr"/>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>trade_not_closed</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -8499,6 +8539,11 @@
       </c>
       <c r="S452" t="inlineStr"/>
       <c r="T452" t="inlineStr"/>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>trade_not_closed</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -8569,6 +8614,9 @@
       </c>
       <c r="S453" t="inlineStr"/>
       <c r="T453" t="inlineStr"/>
+      <c r="U453" t="n">
+        <v>0.6383999999999901</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -8635,6 +8683,9 @@
       </c>
       <c r="S454" t="inlineStr"/>
       <c r="T454" t="inlineStr"/>
+      <c r="U454" t="n">
+        <v>1.451599999999985</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -8707,6 +8758,9 @@
       </c>
       <c r="S455" t="inlineStr"/>
       <c r="T455" t="inlineStr"/>
+      <c r="U455" t="n">
+        <v>-0.6383999999999901</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="inlineStr">

--- a/daily_analysis_combined.xlsx
+++ b/daily_analysis_combined.xlsx
@@ -1208,12 +1208,12 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>sell_triggered</t>
+          <t>sell_triggered_329.0192_buyback_profit_1</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>329.0192 buyback_profit_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -1224,7 +1224,7 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="n">
-        <v>0.6424000000000092</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="61">
@@ -1276,20 +1276,16 @@
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>sell_triggered</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>328.5 buyback_profit_2_1 ( error1)</t>
-        </is>
-      </c>
+          <t>sell_triggered_328.5_buyback_profit_2_1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="n">
-        <v>0.5192000000000121</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="62">
@@ -1403,12 +1399,12 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>sell_triggered</t>
+          <t>sell_triggered_327.2416_buyback_profit_3_1</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>328.5 stop_loss_3_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -1429,7 +1425,7 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="n">
-        <v>-0.5192000000000121</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="64">
@@ -1506,7 +1502,7 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="n">
-        <v>-1.038400000000024</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="65">
@@ -1555,12 +1551,12 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>sell_triggered</t>
+          <t>sell_triggered_327.9808_stop_loss_4</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>327.9808 stop_loss_4</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -1581,7 +1577,7 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="n">
-        <v>-0.7391999999999825</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="66">
@@ -2398,21 +2394,33 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
+          <t>buy_triggered_328.552532_stop_loss_1</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>331.73699999999997 sell_profit_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="n">
-        <v>2.16</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="126">
@@ -2463,12 +2471,12 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_328.552532_stop_loss_2_1</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>330.4 sell_profit_2_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -2489,7 +2497,7 @@
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="n">
-        <v>1.34</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="127">
@@ -2694,12 +2702,12 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_329.063_sell_profit_3_2</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>329.063 sell_profit_3_2</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -4778,12 +4786,12 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_330.624684_stop_loss_1</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>330.624684 stop_loss_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -4855,12 +4863,12 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_330.624684_stop_loss_2_1</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>330.624684 stop_loss_2_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -4932,12 +4940,12 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_330.040584_stop_loss_2_2</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>330.040584 stop_loss_2_2</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
@@ -5009,13 +5017,17 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="O258" t="inlineStr"/>
+          <t>buy_triggered_328.9815_stop_loss_3_1</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>331.938 sell_profit_3_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
@@ -5031,7 +5043,7 @@
       <c r="S258" t="inlineStr"/>
       <c r="T258" t="inlineStr"/>
       <c r="U258" t="n">
-        <v>1.72</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="259">
@@ -5082,13 +5094,17 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="O259" t="inlineStr"/>
+          <t>buy_triggered_328.9815_stop_loss_3_2</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>331.281 sell_profit_3_2</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
@@ -5104,7 +5120,7 @@
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr"/>
       <c r="U259" t="n">
-        <v>1.06</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="260">
@@ -5153,13 +5169,17 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="O260" t="inlineStr"/>
+          <t>buy_triggered_328.5_stop_loss_4</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>330.75 sell_profit_4</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
@@ -5175,7 +5195,7 @@
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr"/>
       <c r="U260" t="n">
-        <v>1.29</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="261">
@@ -5992,12 +6012,12 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_331.27455760000004_stop_loss_1</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>331.27455760000004 stop_loss_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">
@@ -6069,15 +6089,19 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_331.27455760000004_stop_loss_2_1</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>331.27455760000004 stop_loss_2_1</t>
-        </is>
-      </c>
-      <c r="P321" t="inlineStr"/>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
       <c r="Q321" t="inlineStr">
         <is>
           <t>trade_closed</t>
@@ -6142,14 +6166,22 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="O322" t="inlineStr"/>
-      <c r="P322" t="inlineStr"/>
+          <t>buy_triggered_330.4568176_stop_loss_2_2</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>330.4568176 stop_loss_2_2</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -6211,12 +6243,12 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_328.9741_stop_loss_3_1</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>333.1132 sell_profit_3_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
@@ -6237,7 +6269,7 @@
       <c r="S323" t="inlineStr"/>
       <c r="T323" t="inlineStr"/>
       <c r="U323" t="n">
-        <v>2.41</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="324">
@@ -6288,12 +6320,12 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_328.9741_stop_loss_3_2</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>332.1934 sell_profit_3_2</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
@@ -6314,7 +6346,7 @@
       <c r="S324" t="inlineStr"/>
       <c r="T324" t="inlineStr"/>
       <c r="U324" t="n">
-        <v>1.49</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="325">
@@ -6363,12 +6395,12 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_331.45000000000005_sell_profit_4</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>331.45000000000005 sell_profit_4</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P325" t="inlineStr">
@@ -7206,12 +7238,12 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_331.4440512_stop_loss_1</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>331.4440512 stop_loss_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P385" t="inlineStr">
@@ -7283,12 +7315,12 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_331.4440512_stop_loss_2_1</t>
         </is>
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>331.4440512 stop_loss_2_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P386" t="inlineStr">
@@ -7360,12 +7392,12 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_330.7171712_stop_loss_2_2</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>330.7171712 stop_loss_2_2</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
@@ -7437,15 +7469,27 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="O388" t="inlineStr"/>
-      <c r="P388" t="inlineStr"/>
-      <c r="Q388" t="inlineStr"/>
+          <t>buy_triggered_329.3992_stop_loss_3_1</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
       <c r="R388" t="inlineStr">
         <is>
-          <t>329.3992 stop_loss_3_1</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="S388" t="inlineStr"/>
@@ -7502,15 +7546,27 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
-        </is>
-      </c>
-      <c r="O389" t="inlineStr"/>
-      <c r="P389" t="inlineStr"/>
-      <c r="Q389" t="inlineStr"/>
+          <t>buy_triggered_329.3992_stop_loss_3_2</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>trade_closed</t>
+        </is>
+      </c>
       <c r="R389" t="inlineStr">
         <is>
-          <t>329.3992 stop_loss_3_2</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="S389" t="inlineStr"/>
@@ -7565,12 +7621,12 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t>buy_triggered</t>
+          <t>buy_triggered_331.6_sell_profit_4</t>
         </is>
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>331.6 sell_profit_4</t>
+          <t>trade_closed</t>
         </is>
       </c>
       <c r="P390" t="inlineStr">
@@ -8471,15 +8527,13 @@
       <c r="Q451" t="inlineStr"/>
       <c r="R451" t="inlineStr">
         <is>
-          <t>sell_triggered</t>
+          <t>sell_triggered_330.6_buyback_profit_2_1</t>
         </is>
       </c>
       <c r="S451" t="inlineStr"/>
       <c r="T451" t="inlineStr"/>
-      <c r="U451" t="inlineStr">
-        <is>
-          <t>trade_not_closed</t>
-        </is>
+      <c r="U451" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="452">
@@ -8594,14 +8648,10 @@
       <c r="N453" t="inlineStr"/>
       <c r="O453" t="inlineStr">
         <is>
-          <t>sell_triggered</t>
-        </is>
-      </c>
-      <c r="P453" t="inlineStr">
-        <is>
-          <t>329.5132 buyback_profit_3_1 ( error1)</t>
-        </is>
-      </c>
+          <t>sell_triggered_329.5132_buyback_profit_3_1</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr"/>
       <c r="Q453" t="inlineStr">
         <is>
           <t>trade_closed</t>
@@ -8615,7 +8665,7 @@
       <c r="S453" t="inlineStr"/>
       <c r="T453" t="inlineStr"/>
       <c r="U453" t="n">
-        <v>0.6383999999999901</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="454">
@@ -8684,7 +8734,7 @@
       <c r="S454" t="inlineStr"/>
       <c r="T454" t="inlineStr"/>
       <c r="U454" t="n">
-        <v>1.451599999999985</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="455">
@@ -8759,7 +8809,7 @@
       <c r="S455" t="inlineStr"/>
       <c r="T455" t="inlineStr"/>
       <c r="U455" t="n">
-        <v>-0.6383999999999901</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="456">
